--- a/BWI/bestwine_output/bestwine_Greece.xlsx
+++ b/BWI/bestwine_output/bestwine_Greece.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA466"/>
+  <dimension ref="A1:AA468"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -49790,6 +49790,204 @@
       <c r="Z466" s="2" t="inlineStr"/>
       <c r="AA466" s="2" t="inlineStr"/>
     </row>
+    <row r="467">
+      <c r="A467" s="2" t="inlineStr">
+        <is>
+          <t>Tzortzatos, Spyridon, Sole Shareholder Co. Ltd</t>
+        </is>
+      </c>
+      <c r="B467" s="2" t="inlineStr">
+        <is>
+          <t>Tzortzatos, Spyridon, Sole Shareholder Co. Ltd</t>
+        </is>
+      </c>
+      <c r="C467" s="2" t="inlineStr">
+        <is>
+          <t>49453</t>
+        </is>
+      </c>
+      <c r="D467" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E467" s="2" t="inlineStr">
+        <is>
+          <t>Kassopaia Municipal Unit</t>
+        </is>
+      </c>
+      <c r="F467" s="2" t="inlineStr">
+        <is>
+          <t>Ioanian Islands</t>
+        </is>
+      </c>
+      <c r="G467" s="2" t="inlineStr">
+        <is>
+          <t>Sinion Oil Production</t>
+        </is>
+      </c>
+      <c r="H467" s="2" t="inlineStr">
+        <is>
+          <t>491 00</t>
+        </is>
+      </c>
+      <c r="I467" s="2" t="inlineStr">
+        <is>
+          <t>https://cavatzortzatos.gr</t>
+        </is>
+      </c>
+      <c r="J467" s="2" t="inlineStr"/>
+      <c r="K467" s="2" t="inlineStr"/>
+      <c r="L467" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M467" s="2" t="inlineStr"/>
+      <c r="N467" s="2" t="inlineStr">
+        <is>
+          <t>shop@cavatzortzatos.gr</t>
+        </is>
+      </c>
+      <c r="O467" s="2" t="inlineStr">
+        <is>
+          <t>+30 2663 029240</t>
+        </is>
+      </c>
+      <c r="P467" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q467" s="2" t="inlineStr">
+        <is>
+          <t>999776607</t>
+        </is>
+      </c>
+      <c r="R467" s="2" t="inlineStr"/>
+      <c r="S467" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cavatzortzatos/</t>
+        </is>
+      </c>
+      <c r="T467" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cava_tzortzatos/</t>
+        </is>
+      </c>
+      <c r="U467" s="2" t="inlineStr"/>
+      <c r="V467" s="2" t="inlineStr"/>
+      <c r="W467" s="2" t="inlineStr"/>
+      <c r="X467" s="2" t="inlineStr"/>
+      <c r="Y467" s="2" t="inlineStr"/>
+      <c r="Z467" s="2" t="inlineStr"/>
+      <c r="AA467" s="2" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="2" t="inlineStr">
+        <is>
+          <t>Winebox Fine Wine Merchants</t>
+        </is>
+      </c>
+      <c r="B468" s="2" t="inlineStr">
+        <is>
+          <t>Winebox Fine Wine Merchants</t>
+        </is>
+      </c>
+      <c r="C468" s="2" t="inlineStr">
+        <is>
+          <t>7406</t>
+        </is>
+      </c>
+      <c r="D468" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E468" s="2" t="inlineStr">
+        <is>
+          <t>Athens</t>
+        </is>
+      </c>
+      <c r="F468" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G468" s="2" t="inlineStr">
+        <is>
+          <t>25 Xenokratous</t>
+        </is>
+      </c>
+      <c r="H468" s="2" t="inlineStr">
+        <is>
+          <t>106 76</t>
+        </is>
+      </c>
+      <c r="I468" s="2" t="inlineStr">
+        <is>
+          <t>https://winebox.gr</t>
+        </is>
+      </c>
+      <c r="J468" s="2" t="inlineStr"/>
+      <c r="K468" s="2" t="inlineStr"/>
+      <c r="L468" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M468" s="2" t="inlineStr"/>
+      <c r="N468" s="2" t="inlineStr">
+        <is>
+          <t>info@winebox.gr</t>
+        </is>
+      </c>
+      <c r="O468" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0725 4710</t>
+        </is>
+      </c>
+      <c r="P468" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q468" s="2" t="inlineStr">
+        <is>
+          <t>997507461</t>
+        </is>
+      </c>
+      <c r="R468" s="2" t="inlineStr"/>
+      <c r="S468" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/thewinebox-fine-wine-merchants-374672247948/</t>
+        </is>
+      </c>
+      <c r="T468" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winebox.gr/</t>
+        </is>
+      </c>
+      <c r="U468" s="2" t="inlineStr"/>
+      <c r="V468" s="2" t="inlineStr"/>
+      <c r="W468" s="2" t="inlineStr">
+        <is>
+          <t>Alexandros Bari</t>
+        </is>
+      </c>
+      <c r="X468" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y468" s="2" t="inlineStr"/>
+      <c r="Z468" s="2" t="inlineStr"/>
+      <c r="AA468" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alexandros-bari-62a212/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Greece.xlsx
+++ b/BWI/bestwine_output/bestwine_Greece.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA468"/>
+  <dimension ref="A1:AA470"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -49988,6 +49988,204 @@
         </is>
       </c>
     </row>
+    <row r="469">
+      <c r="A469" s="2" t="inlineStr">
+        <is>
+          <t>Tzortzatos, Spyridon, Sole Shareholder Co. Ltd</t>
+        </is>
+      </c>
+      <c r="B469" s="2" t="inlineStr">
+        <is>
+          <t>Tzortzatos, Spyridon, Sole Shareholder Co. Ltd</t>
+        </is>
+      </c>
+      <c r="C469" s="2" t="inlineStr">
+        <is>
+          <t>49453</t>
+        </is>
+      </c>
+      <c r="D469" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E469" s="2" t="inlineStr">
+        <is>
+          <t>Kassopaia Municipal Unit</t>
+        </is>
+      </c>
+      <c r="F469" s="2" t="inlineStr">
+        <is>
+          <t>Ioanian Islands</t>
+        </is>
+      </c>
+      <c r="G469" s="2" t="inlineStr">
+        <is>
+          <t>Sinion Oil Production</t>
+        </is>
+      </c>
+      <c r="H469" s="2" t="inlineStr">
+        <is>
+          <t>491 00</t>
+        </is>
+      </c>
+      <c r="I469" s="2" t="inlineStr">
+        <is>
+          <t>https://cavatzortzatos.gr</t>
+        </is>
+      </c>
+      <c r="J469" s="2" t="inlineStr"/>
+      <c r="K469" s="2" t="inlineStr"/>
+      <c r="L469" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M469" s="2" t="inlineStr"/>
+      <c r="N469" s="2" t="inlineStr">
+        <is>
+          <t>shop@cavatzortzatos.gr</t>
+        </is>
+      </c>
+      <c r="O469" s="2" t="inlineStr">
+        <is>
+          <t>+30 2663 029240</t>
+        </is>
+      </c>
+      <c r="P469" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q469" s="2" t="inlineStr">
+        <is>
+          <t>999776607</t>
+        </is>
+      </c>
+      <c r="R469" s="2" t="inlineStr"/>
+      <c r="S469" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cavatzortzatos/</t>
+        </is>
+      </c>
+      <c r="T469" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cava_tzortzatos/</t>
+        </is>
+      </c>
+      <c r="U469" s="2" t="inlineStr"/>
+      <c r="V469" s="2" t="inlineStr"/>
+      <c r="W469" s="2" t="inlineStr"/>
+      <c r="X469" s="2" t="inlineStr"/>
+      <c r="Y469" s="2" t="inlineStr"/>
+      <c r="Z469" s="2" t="inlineStr"/>
+      <c r="AA469" s="2" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="2" t="inlineStr">
+        <is>
+          <t>Winebox Fine Wine Merchants</t>
+        </is>
+      </c>
+      <c r="B470" s="2" t="inlineStr">
+        <is>
+          <t>Winebox Fine Wine Merchants</t>
+        </is>
+      </c>
+      <c r="C470" s="2" t="inlineStr">
+        <is>
+          <t>7406</t>
+        </is>
+      </c>
+      <c r="D470" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E470" s="2" t="inlineStr">
+        <is>
+          <t>Athens</t>
+        </is>
+      </c>
+      <c r="F470" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G470" s="2" t="inlineStr">
+        <is>
+          <t>25 Xenokratous</t>
+        </is>
+      </c>
+      <c r="H470" s="2" t="inlineStr">
+        <is>
+          <t>106 76</t>
+        </is>
+      </c>
+      <c r="I470" s="2" t="inlineStr">
+        <is>
+          <t>https://winebox.gr</t>
+        </is>
+      </c>
+      <c r="J470" s="2" t="inlineStr"/>
+      <c r="K470" s="2" t="inlineStr"/>
+      <c r="L470" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M470" s="2" t="inlineStr"/>
+      <c r="N470" s="2" t="inlineStr">
+        <is>
+          <t>info@winebox.gr</t>
+        </is>
+      </c>
+      <c r="O470" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0725 4710</t>
+        </is>
+      </c>
+      <c r="P470" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q470" s="2" t="inlineStr">
+        <is>
+          <t>997507461</t>
+        </is>
+      </c>
+      <c r="R470" s="2" t="inlineStr"/>
+      <c r="S470" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/thewinebox-fine-wine-merchants-374672247948/</t>
+        </is>
+      </c>
+      <c r="T470" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winebox.gr/</t>
+        </is>
+      </c>
+      <c r="U470" s="2" t="inlineStr"/>
+      <c r="V470" s="2" t="inlineStr"/>
+      <c r="W470" s="2" t="inlineStr">
+        <is>
+          <t>Alexandros Bari</t>
+        </is>
+      </c>
+      <c r="X470" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y470" s="2" t="inlineStr"/>
+      <c r="Z470" s="2" t="inlineStr"/>
+      <c r="AA470" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alexandros-bari-62a212/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Greece.xlsx
+++ b/BWI/bestwine_output/bestwine_Greece.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA470"/>
+  <dimension ref="A1:AA475"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -50186,6 +50186,519 @@
         </is>
       </c>
     </row>
+    <row r="471">
+      <c r="A471" s="2" t="inlineStr">
+        <is>
+          <t>Tsiakalakis, G., - J. Temertzoglou S.a.</t>
+        </is>
+      </c>
+      <c r="B471" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cava Nectar S.A. </t>
+        </is>
+      </c>
+      <c r="C471" s="2" t="inlineStr">
+        <is>
+          <t>100186</t>
+        </is>
+      </c>
+      <c r="D471" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E471" s="2" t="inlineStr">
+        <is>
+          <t>Athens</t>
+        </is>
+      </c>
+      <c r="F471" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G471" s="2" t="inlineStr">
+        <is>
+          <t>121 Ermou</t>
+        </is>
+      </c>
+      <c r="H471" s="2" t="inlineStr">
+        <is>
+          <t>105 55</t>
+        </is>
+      </c>
+      <c r="I471" s="2" t="inlineStr">
+        <is>
+          <t>https://cavanektar.gr, https://eshop.cavanektar.gr</t>
+        </is>
+      </c>
+      <c r="J471" s="2" t="inlineStr"/>
+      <c r="K471" s="2" t="inlineStr"/>
+      <c r="L471" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="M471" s="2" t="inlineStr"/>
+      <c r="N471" s="2" t="inlineStr">
+        <is>
+          <t>retail.ermou@kavanektar.gr</t>
+        </is>
+      </c>
+      <c r="O471" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0322 2216</t>
+        </is>
+      </c>
+      <c r="P471" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q471" s="2" t="inlineStr">
+        <is>
+          <t>081142850</t>
+        </is>
+      </c>
+      <c r="R471" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cava-nektar-s-a/</t>
+        </is>
+      </c>
+      <c r="S471" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/kavanektar</t>
+        </is>
+      </c>
+      <c r="T471" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cava_nektar</t>
+        </is>
+      </c>
+      <c r="U471" s="2" t="inlineStr"/>
+      <c r="V471" s="2" t="inlineStr"/>
+      <c r="W471" s="2" t="inlineStr">
+        <is>
+          <t>Nikos Triantafyllakis</t>
+        </is>
+      </c>
+      <c r="X471" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y471" s="2" t="inlineStr"/>
+      <c r="Z471" s="2" t="inlineStr"/>
+      <c r="AA471" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nikos-triantafyllakis-21793224b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" s="2" t="inlineStr">
+        <is>
+          <t>Tsiakalakis, G., - J. Temertzoglou S.a.</t>
+        </is>
+      </c>
+      <c r="B472" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cava Nectar S.A. </t>
+        </is>
+      </c>
+      <c r="C472" s="2" t="inlineStr">
+        <is>
+          <t>100186</t>
+        </is>
+      </c>
+      <c r="D472" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E472" s="2" t="inlineStr">
+        <is>
+          <t>Athens</t>
+        </is>
+      </c>
+      <c r="F472" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G472" s="2" t="inlineStr">
+        <is>
+          <t>121 Ermou</t>
+        </is>
+      </c>
+      <c r="H472" s="2" t="inlineStr">
+        <is>
+          <t>105 55</t>
+        </is>
+      </c>
+      <c r="I472" s="2" t="inlineStr">
+        <is>
+          <t>https://cavanektar.gr, https://eshop.cavanektar.gr</t>
+        </is>
+      </c>
+      <c r="J472" s="2" t="inlineStr"/>
+      <c r="K472" s="2" t="inlineStr"/>
+      <c r="L472" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="M472" s="2" t="inlineStr"/>
+      <c r="N472" s="2" t="inlineStr">
+        <is>
+          <t>retail.ermou@kavanektar.gr</t>
+        </is>
+      </c>
+      <c r="O472" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0322 2216</t>
+        </is>
+      </c>
+      <c r="P472" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q472" s="2" t="inlineStr">
+        <is>
+          <t>081142850</t>
+        </is>
+      </c>
+      <c r="R472" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cava-nektar-s-a/</t>
+        </is>
+      </c>
+      <c r="S472" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/kavanektar</t>
+        </is>
+      </c>
+      <c r="T472" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cava_nektar</t>
+        </is>
+      </c>
+      <c r="U472" s="2" t="inlineStr"/>
+      <c r="V472" s="2" t="inlineStr"/>
+      <c r="W472" s="2" t="inlineStr">
+        <is>
+          <t>Zacharias Bithimitris</t>
+        </is>
+      </c>
+      <c r="X472" s="2" t="inlineStr">
+        <is>
+          <t>Retail Manager</t>
+        </is>
+      </c>
+      <c r="Y472" s="2" t="inlineStr"/>
+      <c r="Z472" s="2" t="inlineStr"/>
+      <c r="AA472" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/zacharias-bithimitris-41682548/</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" s="2" t="inlineStr">
+        <is>
+          <t>Yannis Market</t>
+        </is>
+      </c>
+      <c r="B473" s="2" t="inlineStr">
+        <is>
+          <t>Yannis Market</t>
+        </is>
+      </c>
+      <c r="C473" s="2" t="inlineStr">
+        <is>
+          <t>104673</t>
+        </is>
+      </c>
+      <c r="D473" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E473" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Northern Corfu</t>
+        </is>
+      </c>
+      <c r="F473" s="2" t="inlineStr">
+        <is>
+          <t>Ioanian Islands</t>
+        </is>
+      </c>
+      <c r="G473" s="2" t="inlineStr">
+        <is>
+          <t>Agnitisini Sinies</t>
+        </is>
+      </c>
+      <c r="H473" s="2" t="inlineStr">
+        <is>
+          <t>490 81</t>
+        </is>
+      </c>
+      <c r="I473" s="2" t="inlineStr">
+        <is>
+          <t>http://yannismarket.com</t>
+        </is>
+      </c>
+      <c r="J473" s="2" t="inlineStr"/>
+      <c r="K473" s="2" t="inlineStr"/>
+      <c r="L473" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M473" s="2" t="inlineStr"/>
+      <c r="N473" s="2" t="inlineStr">
+        <is>
+          <t>i.garnelis@gmail.com</t>
+        </is>
+      </c>
+      <c r="O473" s="2" t="inlineStr">
+        <is>
+          <t>+30 2663 029230</t>
+        </is>
+      </c>
+      <c r="P473" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q473" s="2" t="inlineStr">
+        <is>
+          <t>47968403</t>
+        </is>
+      </c>
+      <c r="R473" s="2" t="inlineStr"/>
+      <c r="S473" s="2" t="inlineStr"/>
+      <c r="T473" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yannisdelicatessen1920/</t>
+        </is>
+      </c>
+      <c r="U473" s="2" t="inlineStr"/>
+      <c r="V473" s="2" t="inlineStr"/>
+      <c r="W473" s="2" t="inlineStr">
+        <is>
+          <t>Yannis Garnelis</t>
+        </is>
+      </c>
+      <c r="X473" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y473" s="2" t="inlineStr"/>
+      <c r="Z473" s="2" t="inlineStr"/>
+      <c r="AA473" s="2" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" s="2" t="inlineStr">
+        <is>
+          <t>Tzortzatos, Spyridon, Sole Shareholder Co. Ltd</t>
+        </is>
+      </c>
+      <c r="B474" s="2" t="inlineStr">
+        <is>
+          <t>Tzortzatos, Spyridon, Sole Shareholder Co. Ltd</t>
+        </is>
+      </c>
+      <c r="C474" s="2" t="inlineStr">
+        <is>
+          <t>49453</t>
+        </is>
+      </c>
+      <c r="D474" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E474" s="2" t="inlineStr">
+        <is>
+          <t>Kassopaia Municipal Unit</t>
+        </is>
+      </c>
+      <c r="F474" s="2" t="inlineStr">
+        <is>
+          <t>Ioanian Islands</t>
+        </is>
+      </c>
+      <c r="G474" s="2" t="inlineStr">
+        <is>
+          <t>Sinion Oil Production</t>
+        </is>
+      </c>
+      <c r="H474" s="2" t="inlineStr">
+        <is>
+          <t>491 00</t>
+        </is>
+      </c>
+      <c r="I474" s="2" t="inlineStr">
+        <is>
+          <t>https://cavatzortzatos.gr</t>
+        </is>
+      </c>
+      <c r="J474" s="2" t="inlineStr"/>
+      <c r="K474" s="2" t="inlineStr"/>
+      <c r="L474" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M474" s="2" t="inlineStr"/>
+      <c r="N474" s="2" t="inlineStr">
+        <is>
+          <t>shop@cavatzortzatos.gr</t>
+        </is>
+      </c>
+      <c r="O474" s="2" t="inlineStr">
+        <is>
+          <t>+30 2663 029240</t>
+        </is>
+      </c>
+      <c r="P474" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q474" s="2" t="inlineStr">
+        <is>
+          <t>999776607</t>
+        </is>
+      </c>
+      <c r="R474" s="2" t="inlineStr"/>
+      <c r="S474" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cavatzortzatos/</t>
+        </is>
+      </c>
+      <c r="T474" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cava_tzortzatos/</t>
+        </is>
+      </c>
+      <c r="U474" s="2" t="inlineStr"/>
+      <c r="V474" s="2" t="inlineStr"/>
+      <c r="W474" s="2" t="inlineStr"/>
+      <c r="X474" s="2" t="inlineStr"/>
+      <c r="Y474" s="2" t="inlineStr"/>
+      <c r="Z474" s="2" t="inlineStr"/>
+      <c r="AA474" s="2" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="2" t="inlineStr">
+        <is>
+          <t>Winebox Fine Wine Merchants</t>
+        </is>
+      </c>
+      <c r="B475" s="2" t="inlineStr">
+        <is>
+          <t>Winebox Fine Wine Merchants</t>
+        </is>
+      </c>
+      <c r="C475" s="2" t="inlineStr">
+        <is>
+          <t>7406</t>
+        </is>
+      </c>
+      <c r="D475" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E475" s="2" t="inlineStr">
+        <is>
+          <t>Athens</t>
+        </is>
+      </c>
+      <c r="F475" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G475" s="2" t="inlineStr">
+        <is>
+          <t>25 Xenokratous</t>
+        </is>
+      </c>
+      <c r="H475" s="2" t="inlineStr">
+        <is>
+          <t>106 76</t>
+        </is>
+      </c>
+      <c r="I475" s="2" t="inlineStr">
+        <is>
+          <t>https://winebox.gr</t>
+        </is>
+      </c>
+      <c r="J475" s="2" t="inlineStr"/>
+      <c r="K475" s="2" t="inlineStr"/>
+      <c r="L475" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M475" s="2" t="inlineStr"/>
+      <c r="N475" s="2" t="inlineStr">
+        <is>
+          <t>info@winebox.gr</t>
+        </is>
+      </c>
+      <c r="O475" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0725 4710</t>
+        </is>
+      </c>
+      <c r="P475" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q475" s="2" t="inlineStr">
+        <is>
+          <t>997507461</t>
+        </is>
+      </c>
+      <c r="R475" s="2" t="inlineStr"/>
+      <c r="S475" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/thewinebox-fine-wine-merchants-374672247948/</t>
+        </is>
+      </c>
+      <c r="T475" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winebox.gr/</t>
+        </is>
+      </c>
+      <c r="U475" s="2" t="inlineStr"/>
+      <c r="V475" s="2" t="inlineStr"/>
+      <c r="W475" s="2" t="inlineStr">
+        <is>
+          <t>Alexandros Bari</t>
+        </is>
+      </c>
+      <c r="X475" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y475" s="2" t="inlineStr"/>
+      <c r="Z475" s="2" t="inlineStr"/>
+      <c r="AA475" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alexandros-bari-62a212/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Greece.xlsx
+++ b/BWI/bestwine_output/bestwine_Greece.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA475"/>
+  <dimension ref="A1:AA480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -50699,6 +50699,519 @@
         </is>
       </c>
     </row>
+    <row r="476">
+      <c r="A476" s="2" t="inlineStr">
+        <is>
+          <t>Tsiakalakis, G., - J. Temertzoglou S.a.</t>
+        </is>
+      </c>
+      <c r="B476" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cava Nectar S.A. </t>
+        </is>
+      </c>
+      <c r="C476" s="2" t="inlineStr">
+        <is>
+          <t>100186</t>
+        </is>
+      </c>
+      <c r="D476" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E476" s="2" t="inlineStr">
+        <is>
+          <t>Athens</t>
+        </is>
+      </c>
+      <c r="F476" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G476" s="2" t="inlineStr">
+        <is>
+          <t>121 Ermou</t>
+        </is>
+      </c>
+      <c r="H476" s="2" t="inlineStr">
+        <is>
+          <t>105 55</t>
+        </is>
+      </c>
+      <c r="I476" s="2" t="inlineStr">
+        <is>
+          <t>https://cavanektar.gr, https://eshop.cavanektar.gr</t>
+        </is>
+      </c>
+      <c r="J476" s="2" t="inlineStr"/>
+      <c r="K476" s="2" t="inlineStr"/>
+      <c r="L476" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="M476" s="2" t="inlineStr"/>
+      <c r="N476" s="2" t="inlineStr">
+        <is>
+          <t>retail.ermou@kavanektar.gr</t>
+        </is>
+      </c>
+      <c r="O476" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0322 2216</t>
+        </is>
+      </c>
+      <c r="P476" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q476" s="2" t="inlineStr">
+        <is>
+          <t>081142850</t>
+        </is>
+      </c>
+      <c r="R476" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cava-nektar-s-a/</t>
+        </is>
+      </c>
+      <c r="S476" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/kavanektar</t>
+        </is>
+      </c>
+      <c r="T476" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cava_nektar</t>
+        </is>
+      </c>
+      <c r="U476" s="2" t="inlineStr"/>
+      <c r="V476" s="2" t="inlineStr"/>
+      <c r="W476" s="2" t="inlineStr">
+        <is>
+          <t>Nikos Triantafyllakis</t>
+        </is>
+      </c>
+      <c r="X476" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y476" s="2" t="inlineStr"/>
+      <c r="Z476" s="2" t="inlineStr"/>
+      <c r="AA476" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nikos-triantafyllakis-21793224b/</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" s="2" t="inlineStr">
+        <is>
+          <t>Tsiakalakis, G., - J. Temertzoglou S.a.</t>
+        </is>
+      </c>
+      <c r="B477" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cava Nectar S.A. </t>
+        </is>
+      </c>
+      <c r="C477" s="2" t="inlineStr">
+        <is>
+          <t>100186</t>
+        </is>
+      </c>
+      <c r="D477" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E477" s="2" t="inlineStr">
+        <is>
+          <t>Athens</t>
+        </is>
+      </c>
+      <c r="F477" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G477" s="2" t="inlineStr">
+        <is>
+          <t>121 Ermou</t>
+        </is>
+      </c>
+      <c r="H477" s="2" t="inlineStr">
+        <is>
+          <t>105 55</t>
+        </is>
+      </c>
+      <c r="I477" s="2" t="inlineStr">
+        <is>
+          <t>https://cavanektar.gr, https://eshop.cavanektar.gr</t>
+        </is>
+      </c>
+      <c r="J477" s="2" t="inlineStr"/>
+      <c r="K477" s="2" t="inlineStr"/>
+      <c r="L477" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="M477" s="2" t="inlineStr"/>
+      <c r="N477" s="2" t="inlineStr">
+        <is>
+          <t>retail.ermou@kavanektar.gr</t>
+        </is>
+      </c>
+      <c r="O477" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0322 2216</t>
+        </is>
+      </c>
+      <c r="P477" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q477" s="2" t="inlineStr">
+        <is>
+          <t>081142850</t>
+        </is>
+      </c>
+      <c r="R477" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/cava-nektar-s-a/</t>
+        </is>
+      </c>
+      <c r="S477" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/kavanektar</t>
+        </is>
+      </c>
+      <c r="T477" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cava_nektar</t>
+        </is>
+      </c>
+      <c r="U477" s="2" t="inlineStr"/>
+      <c r="V477" s="2" t="inlineStr"/>
+      <c r="W477" s="2" t="inlineStr">
+        <is>
+          <t>Zacharias Bithimitris</t>
+        </is>
+      </c>
+      <c r="X477" s="2" t="inlineStr">
+        <is>
+          <t>Retail Manager</t>
+        </is>
+      </c>
+      <c r="Y477" s="2" t="inlineStr"/>
+      <c r="Z477" s="2" t="inlineStr"/>
+      <c r="AA477" s="2" t="inlineStr">
+        <is>
+          <t>Https://www.linkedin.com/in/zacharias-bithimitris-41682548/</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" s="2" t="inlineStr">
+        <is>
+          <t>Yannis Market</t>
+        </is>
+      </c>
+      <c r="B478" s="2" t="inlineStr">
+        <is>
+          <t>Yannis Market</t>
+        </is>
+      </c>
+      <c r="C478" s="2" t="inlineStr">
+        <is>
+          <t>104673</t>
+        </is>
+      </c>
+      <c r="D478" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E478" s="2" t="inlineStr">
+        <is>
+          <t>Municipality of Northern Corfu</t>
+        </is>
+      </c>
+      <c r="F478" s="2" t="inlineStr">
+        <is>
+          <t>Ioanian Islands</t>
+        </is>
+      </c>
+      <c r="G478" s="2" t="inlineStr">
+        <is>
+          <t>Agnitisini Sinies</t>
+        </is>
+      </c>
+      <c r="H478" s="2" t="inlineStr">
+        <is>
+          <t>490 81</t>
+        </is>
+      </c>
+      <c r="I478" s="2" t="inlineStr">
+        <is>
+          <t>http://yannismarket.com</t>
+        </is>
+      </c>
+      <c r="J478" s="2" t="inlineStr"/>
+      <c r="K478" s="2" t="inlineStr"/>
+      <c r="L478" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M478" s="2" t="inlineStr"/>
+      <c r="N478" s="2" t="inlineStr">
+        <is>
+          <t>i.garnelis@gmail.com</t>
+        </is>
+      </c>
+      <c r="O478" s="2" t="inlineStr">
+        <is>
+          <t>+30 2663 029230</t>
+        </is>
+      </c>
+      <c r="P478" s="2" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="Q478" s="2" t="inlineStr">
+        <is>
+          <t>47968403</t>
+        </is>
+      </c>
+      <c r="R478" s="2" t="inlineStr"/>
+      <c r="S478" s="2" t="inlineStr"/>
+      <c r="T478" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/yannisdelicatessen1920/</t>
+        </is>
+      </c>
+      <c r="U478" s="2" t="inlineStr"/>
+      <c r="V478" s="2" t="inlineStr"/>
+      <c r="W478" s="2" t="inlineStr">
+        <is>
+          <t>Yannis Garnelis</t>
+        </is>
+      </c>
+      <c r="X478" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y478" s="2" t="inlineStr"/>
+      <c r="Z478" s="2" t="inlineStr"/>
+      <c r="AA478" s="2" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="2" t="inlineStr">
+        <is>
+          <t>Tzortzatos, Spyridon, Sole Shareholder Co. Ltd</t>
+        </is>
+      </c>
+      <c r="B479" s="2" t="inlineStr">
+        <is>
+          <t>Tzortzatos, Spyridon, Sole Shareholder Co. Ltd</t>
+        </is>
+      </c>
+      <c r="C479" s="2" t="inlineStr">
+        <is>
+          <t>49453</t>
+        </is>
+      </c>
+      <c r="D479" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E479" s="2" t="inlineStr">
+        <is>
+          <t>Kassopaia Municipal Unit</t>
+        </is>
+      </c>
+      <c r="F479" s="2" t="inlineStr">
+        <is>
+          <t>Ioanian Islands</t>
+        </is>
+      </c>
+      <c r="G479" s="2" t="inlineStr">
+        <is>
+          <t>Sinion Oil Production</t>
+        </is>
+      </c>
+      <c r="H479" s="2" t="inlineStr">
+        <is>
+          <t>491 00</t>
+        </is>
+      </c>
+      <c r="I479" s="2" t="inlineStr">
+        <is>
+          <t>https://cavatzortzatos.gr</t>
+        </is>
+      </c>
+      <c r="J479" s="2" t="inlineStr"/>
+      <c r="K479" s="2" t="inlineStr"/>
+      <c r="L479" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M479" s="2" t="inlineStr"/>
+      <c r="N479" s="2" t="inlineStr">
+        <is>
+          <t>shop@cavatzortzatos.gr</t>
+        </is>
+      </c>
+      <c r="O479" s="2" t="inlineStr">
+        <is>
+          <t>+30 2663 029240</t>
+        </is>
+      </c>
+      <c r="P479" s="2" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="Q479" s="2" t="inlineStr">
+        <is>
+          <t>999776607</t>
+        </is>
+      </c>
+      <c r="R479" s="2" t="inlineStr"/>
+      <c r="S479" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/cavatzortzatos/</t>
+        </is>
+      </c>
+      <c r="T479" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cava_tzortzatos/</t>
+        </is>
+      </c>
+      <c r="U479" s="2" t="inlineStr"/>
+      <c r="V479" s="2" t="inlineStr"/>
+      <c r="W479" s="2" t="inlineStr"/>
+      <c r="X479" s="2" t="inlineStr"/>
+      <c r="Y479" s="2" t="inlineStr"/>
+      <c r="Z479" s="2" t="inlineStr"/>
+      <c r="AA479" s="2" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="2" t="inlineStr">
+        <is>
+          <t>Winebox Fine Wine Merchants</t>
+        </is>
+      </c>
+      <c r="B480" s="2" t="inlineStr">
+        <is>
+          <t>Winebox Fine Wine Merchants</t>
+        </is>
+      </c>
+      <c r="C480" s="2" t="inlineStr">
+        <is>
+          <t>7406</t>
+        </is>
+      </c>
+      <c r="D480" s="2" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="E480" s="2" t="inlineStr">
+        <is>
+          <t>Athens</t>
+        </is>
+      </c>
+      <c r="F480" s="2" t="inlineStr">
+        <is>
+          <t>Attica</t>
+        </is>
+      </c>
+      <c r="G480" s="2" t="inlineStr">
+        <is>
+          <t>25 Xenokratous</t>
+        </is>
+      </c>
+      <c r="H480" s="2" t="inlineStr">
+        <is>
+          <t>106 76</t>
+        </is>
+      </c>
+      <c r="I480" s="2" t="inlineStr">
+        <is>
+          <t>https://winebox.gr</t>
+        </is>
+      </c>
+      <c r="J480" s="2" t="inlineStr"/>
+      <c r="K480" s="2" t="inlineStr"/>
+      <c r="L480" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M480" s="2" t="inlineStr"/>
+      <c r="N480" s="2" t="inlineStr">
+        <is>
+          <t>info@winebox.gr</t>
+        </is>
+      </c>
+      <c r="O480" s="2" t="inlineStr">
+        <is>
+          <t>+30 21 0725 4710</t>
+        </is>
+      </c>
+      <c r="P480" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q480" s="2" t="inlineStr">
+        <is>
+          <t>997507461</t>
+        </is>
+      </c>
+      <c r="R480" s="2" t="inlineStr"/>
+      <c r="S480" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/thewinebox-fine-wine-merchants-374672247948/</t>
+        </is>
+      </c>
+      <c r="T480" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winebox.gr/</t>
+        </is>
+      </c>
+      <c r="U480" s="2" t="inlineStr"/>
+      <c r="V480" s="2" t="inlineStr"/>
+      <c r="W480" s="2" t="inlineStr">
+        <is>
+          <t>Alexandros Bari</t>
+        </is>
+      </c>
+      <c r="X480" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y480" s="2" t="inlineStr"/>
+      <c r="Z480" s="2" t="inlineStr"/>
+      <c r="AA480" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alexandros-bari-62a212/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
